--- a/全椒县各行政村抽样比例统计表.xlsx
+++ b/全椒县各行政村抽样比例统计表.xlsx
@@ -571,7 +571,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>统计口径：按行政村统计外业实际抽查农户数占全村总农户数比例 | 达标标准：实际抽样农户数 ≥ 全村农户总数 × 5% (向上取整) | 统计时间：2026年09月19日</t>
+          <t>统计口径：按行政村统计外业实际抽查农户数占全村总农户数比例 | 达标标准：实际抽样农户数 ≥ 全村农户总数 × 5% (向上取整) | 统计时间：2026年09月21日</t>
         </is>
       </c>
     </row>
